--- a/artfynd/A 34515-2024 artfynd.xlsx
+++ b/artfynd/A 34515-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -788,6 +788,112 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>131548880</v>
+      </c>
+      <c r="B3" t="n">
+        <v>101225</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Dimmestorp 350 m SSV om, Nrk</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>488480</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6510870</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Hammar</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Michael Andersson, Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 34515-2024 artfynd.xlsx
+++ b/artfynd/A 34515-2024 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>131548880</v>
       </c>
       <c r="B3" t="n">
-        <v>101225</v>
+        <v>101228</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34515-2024 artfynd.xlsx
+++ b/artfynd/A 34515-2024 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>131548880</v>
       </c>
       <c r="B3" t="n">
-        <v>101228</v>
+        <v>101231</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34515-2024 artfynd.xlsx
+++ b/artfynd/A 34515-2024 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>131548880</v>
       </c>
       <c r="B3" t="n">
-        <v>101231</v>
+        <v>101237</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34515-2024 artfynd.xlsx
+++ b/artfynd/A 34515-2024 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>131548880</v>
       </c>
       <c r="B3" t="n">
-        <v>101237</v>
+        <v>101238</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34515-2024 artfynd.xlsx
+++ b/artfynd/A 34515-2024 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>131548880</v>
       </c>
       <c r="B3" t="n">
-        <v>101238</v>
+        <v>101239</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34515-2024 artfynd.xlsx
+++ b/artfynd/A 34515-2024 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>131548880</v>
       </c>
       <c r="B3" t="n">
-        <v>101239</v>
+        <v>101242</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34515-2024 artfynd.xlsx
+++ b/artfynd/A 34515-2024 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>131548880</v>
       </c>
       <c r="B3" t="n">
-        <v>101242</v>
+        <v>101243</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34515-2024 artfynd.xlsx
+++ b/artfynd/A 34515-2024 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>131548880</v>
       </c>
       <c r="B3" t="n">
-        <v>101243</v>
+        <v>101249</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34515-2024 artfynd.xlsx
+++ b/artfynd/A 34515-2024 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>131548880</v>
       </c>
       <c r="B3" t="n">
-        <v>101249</v>
+        <v>101252</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34515-2024 artfynd.xlsx
+++ b/artfynd/A 34515-2024 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>131548880</v>
       </c>
       <c r="B3" t="n">
-        <v>101252</v>
+        <v>101257</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34515-2024 artfynd.xlsx
+++ b/artfynd/A 34515-2024 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>131548880</v>
       </c>
       <c r="B3" t="n">
-        <v>101257</v>
+        <v>101260</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34515-2024 artfynd.xlsx
+++ b/artfynd/A 34515-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118676829</v>
+        <v>131549020</v>
       </c>
       <c r="B2" t="n">
-        <v>57311</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96441</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,46 +686,41 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102977</v>
+        <v>2668</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Olshammar, Nrk</t>
+          <t>Dimmestorp 350 m SSV om, Nrk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>488476</v>
+        <v>488501</v>
       </c>
       <c r="R2" t="n">
-        <v>6510730</v>
+        <v>6510845</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,17 +744,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -773,28 +758,39 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Granit</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Granite # block i lövskog</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Michael Andersson, Toni Berglund</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131548880</v>
+        <v>118676829</v>
       </c>
       <c r="B3" t="n">
-        <v>101260</v>
+        <v>57947</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,42 +798,43 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>102977</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Dimmestorp 350 m SSV om, Nrk</t>
+          <t>Olshammar, Nrk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>488480</v>
+        <v>488476</v>
       </c>
       <c r="R3" t="n">
-        <v>6510870</v>
+        <v>6510730</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,12 +861,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2024-07-03</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -878,22 +880,127 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>131548880</v>
+      </c>
+      <c r="B4" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Dimmestorp 350 m SSV om, Nrk</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>488480</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6510870</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Hammar</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
           <t>Michael Andersson</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>Michael Andersson, Toni Berglund</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 34515-2024 artfynd.xlsx
+++ b/artfynd/A 34515-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131549020</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -895,6 +905,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118676829</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1001,8 +1016,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131548880</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>